--- a/amc_tracking_status.xlsx
+++ b/amc_tracking_status.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AMC Tracking" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AMC Tracking" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,10 +35,14 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="009C0006"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -49,6 +53,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
         <bgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -70,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -83,6 +93,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -495,28 +508,1409 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>360 ONE Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.360.one/asset/mutual-funds/downloads/</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>downloads\360_ONE_Mutual_Fund_360_ONE_MF_July_2026_Regular_b1a10fc55a.pdf
+downloads\360_ONE_Mutual_Fund_360_ONE_MF_July_2026_3cc67c14cc.pdf</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Abakkus Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.abakkusmf.com/factsheet.html#</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Abakkus_Mutual_Fund_Abakkus_Mutual_Fund_Factsheet_June_2026_a8749aaaae.pdf</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Aditya Birla Sun Life Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://mutualfund.adityabirlacapital.com/forms-and-downloads/factsheets</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Aditya_Birla_Sun_Life_Mutual_Fund_absl-factsheet_july-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Angel One Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.angelonemf.com/downloads</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Angel_One_Mutual_Fund_Factsheet-Angel-One-Mutual-Fund-Schemes-Jun-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>Axis Mutual Fund</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>https://www.axismf.com/downloads</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Axis_Mutual_Fund_Axis_Fund_Factsheet_May_2026.pdf
+downloads\Axis_Mutual_Fund_AxisPassiveFactsheetMay2026.pdf</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Bajaj Finserv Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bajajamc.com/downloads?factsheet</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Bajaj_Finserv_Mutual_Fund_Abridged-Factsheet_July-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Bandhan Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://bandhanmutual.com/downloads/factsheet/all-schemes</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Bandhan_Mutual_Fund_July_2026.pdf</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Bank of India Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.boimf.in/investor-corner</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Bank_of_India_Mutual_Fund_factsheet-june-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Baroda BNP Paribas Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.barodabnpparibasmf.in/downloads/monthly-factsheet</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Baroda_BNP_Paribas_Mutual_Fund_BBNPP_MF_Fund_Facts_June_2026_19016.pdf</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Canara Robeco Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.canararobeco.com/documents/forms-downloads/forms-information-documents/information-documents/factsheets/</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Canara_Robeco_Mutual_Fund_Canara-Robeco-factsheet-as-on-June-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Capitalmind Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://capitalmindmf.com/factsheet.html#</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Capitalmind_Mutual_Fund_Capitalmind_Mutual_Fund_Factsheet_June_2026_89062d34b0.pdf</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Choice Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://choicemf.com/disclosures/factsheets</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Choice_Mutual_Fund_1784279663-choice_mutual_fund_factsheet_full_june_2026.pdf</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>DSP Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dspim.com/downloads?category=Information%20Documents&amp;sub_category=Factsheets</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>downloads\DSP_Mutual_Fund_dsp-factsheet-june-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Edelweiss Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.edelweissmf.com/downloads/factsheets</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Edelweiss_Mutual_Fund_Edelweiss_Factsheet_July2026_20072026185303.pdf</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Franklin Templeton Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.franklintempletonindia.com/downloads/fund-literature</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Franklin_Templeton_Mutual_Fund_Factsheet-as-on-June-30-2026_web.pdf</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Groww Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.growwmf.in/downloads/fact-sheet</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Groww_Mutual_Fund_Monthly Factsheet June 2026.pdf</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>HDFC Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hdfcfund.com/mutual-funds/factsheets</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>downloads\HDFC_Mutual_Fund_HDFC MF Factsheet - June 2026_1.pdf
+downloads\HDFC_Mutual_Fund_HDFC MF Index Solutions Factsheet - June 2026_1.pdf</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Helios Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.heliosmf.in/downloads</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Helios_Mutual_Fund_Helios-Mutual-Fund-Factsheet-Jun26.pdf
+downloads\Helios_Mutual_Fund_Performance-Helios-Factsheet_Jun26.pdf</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>HSBC Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.assetmanagement.hsbc.co.in/en/mutual-funds/investor-resources?Date=&amp;Cap=&amp;Doc=fund-factsheets</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>downloads\HSBC_Mutual_Fund_the-asset-june-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ICICI Prudential Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.icicipruamc.com/media-center/downloads?currentTabFilter=Historical%20Factsheets</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>downloads\ICICI_Prudential_Mutual_Fund_Complete Factsheet June 2026.pdf</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Invesco Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.invescomutualfund.com/literature-forms/factsheets</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Invesco_Mutual_Fund_invesco-mf-factsheet-june-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ITI Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.itiamc.com/downloads</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>downloads\ITI_Mutual_Fund_1783932535-ITI_Factsheet_June_26.pdf</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Jio BlackRock Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jioblackrockamc.com/statutory-disclosure/fund-documents/factsheet</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Jio_BlackRock_Mutual_Fund_jioblackro-me6p3p5b-f6c23d.pdf</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>JM Financial Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jmfinancialmf.com/downloads/Factsheet/Factsheet</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>downloads\JM_Financial_Mutual_Fund_Factsheet July 2026.pdf</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Kotak Mahindra Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kotakmf.com/Information/forms-and-downloads/Factsheet</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>No relevant factsheet PDFs found.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-04 01:26:06</t>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>LIC Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.licmf.com/downloads/factsheet</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>downloads\LIC_Mutual_Fund_lic-mf-factsheet-30th-june-2026-444415505.pdf</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Mahindra Manulife Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mahindramanulife.com/downloads#investor</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Mahindra_Manulife_Mutual_Fund_a3bcdaad-1c36-4959-bb43-94f69a7a286a.pdf</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Mirae Asset Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miraeassetmf.co.in/downloads/factsheet</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Mirae_Asset_Mutual_Fund_passive-factsheet---july-2026.pdf
+downloads\Mirae_Asset_Mutual_Fund_active-factsheet---july-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Motilal Oswal Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.motilaloswalmf.com/downloads/factsheets</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Motilal_Oswal_Mutual_Fund_Most Factsheet June 2026 Active.pdf
+downloads\Motilal_Oswal_Mutual_Fund_Factsheet June 2026 Passive.pdf</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Navi Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>https://navi.com/mutual-fund/downloads/factsheet</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Navi_Mutual_Fund_Passive_Fund_June26_20260713184903.pdf
+downloads\Navi_Mutual_Fund_Active_Fund_June26_20260713184901.pdf</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Nippon India Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>https://mf.nipponindiaim.com/investor-service/downloads/factsheet-portfolio-and-other-disclosures</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Nippon_India_Mutual_Fund_Nippon-FS-JULY-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>NJ Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>https://downloads.njmutualfund.com/downloads.php</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>downloads\NJ_Mutual_Fund_NJ-AMC-Factsheet-June-2026-20260710060515.pdf</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Old Bridge Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>https://oldbridgemf.com/factsheet.html</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Old_Bridge_Mutual_Fund_OLD_BRIDGE_MF_Factsheet_9e86cb1c2f.pdf</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>PGIM India Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pgimindia.com/mutual-funds/forms-and-product-updates/Fund-Factsheet</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>downloads\PGIM_India_Mutual_Fund_Factsheet - June 2026.pdf</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>PPFAS Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>https://amc.ppfas.com/downloads/factsheet/</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>downloads\PPFAS_Mutual_Fund_ppfas-mf-factsheet-for-June-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>quant Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>https://quantmutual.com/downloads/factsheet</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>downloads\quant_Mutual_Fund_quant_Factsheet_-_August_2026.pdf</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Quantum Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.quantumamc.com/factsheets/combined/-1/0/0</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Quantum_Mutual_Fund_ed2d9740-a26e-4f5b-8c6c-d4c102293708.pdf</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Samco Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.samcomf.com/downloads</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Samco_Mutual_Fund_Factsheet-July2026_1785606935.pdf
+downloads\Samco_Mutual_Fund_Factsheet-July2026_1785606935.pdf</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>SBI Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sbimf.com/factsheets</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>downloads\SBI_Mutual_Fund_sbi-mf-passives-(index-etf-fof)-factsheet-june-2026.pdf
+downloads\SBI_Mutual_Fund_all-sbimf-schemes-factsheet-june-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Shriram Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shriramamc.in/factsheet</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Shriram_Mutual_Fund_Factsheet-July-2026-(1).pdf</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Sundaram Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sundarammutual.com/fundwise-factsheet</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Sundaram_Mutual_Fund_Consolidated_Factsheet_7_2026_140726_121722.pdf</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Tata Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tatamutualfund.com/information-documents/factsheets</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Tata_Mutual_Fund_TataMF Factsheet - June 2026 (1).pdf</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Taurus Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taurusmutualfund.com/factsheet</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Taurus_Mutual_Fund_Taurus_Times_June_2026.pdf</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>The Wealth Company Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wealthcompanyamc.in/literature-forms/scheme-documents/factsheets/</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>downloads\The_Wealth_Company_Mutual_Fund_Factsheet_as_on_30_06_2026_1946ab499d.pdf</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Trust Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.trustmf.com/downloads?activeTab=factsheets</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Trust_Mutual_Fund_TRUSTMF FACT_20260723115930.pdf</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Unifi Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>https://unifimf.com/factsheet/</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Unifi_Mutual_Fund_Unifi-MF-Factsheet-June-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Union Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.unionmf.com/about-us/downloads</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Union_Mutual_Fund_factsheet-june-2026.pdf</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>UTI Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.utimf.com/downloads/fact-sheet</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>No relevant factsheet PDFs found.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>WhiteOak Capital Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>https://mf.whiteoakamc.com/resources?resource-type=downloads&amp;category=factsheet&amp;page=1&amp;subCategory=monthly-factsheet</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>downloads\WhiteOak_Capital_Mutual_Fund_Whiteoak_Capital_Factsheet_June2026_fe8fb12141.pdf</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Zerodha Mutual Fund</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zerodhafundhouse.com/resources/fund-documents</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>downloads\Zerodha_Mutual_Fund_FactSheet_May 2026.pdf</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:48:28</t>
         </is>
       </c>
     </row>

--- a/amc_tracking_status.xlsx
+++ b/amc_tracking_status.xlsx
@@ -530,7 +530,7 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -805,13 +805,13 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>downloads\Capitalmind_Mutual_Fund_Capitalmind_Mutual_Fund_Factsheet_June_2026_89062d34b0.pdf</t>
+          <t>downloads\Capitalmind_Mutual_Fund_Capitalmind_Mutual_Fund_Factsheet_July_2026_d430bc0063.pdf</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -973,14 +973,14 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>downloads\HDFC_Mutual_Fund_HDFC MF Factsheet - June 2026_1.pdf
+          <t>downloads\HDFC_Mutual_Fund_HDFC MF Factsheet - June 2026.pdf
 downloads\HDFC_Mutual_Fund_HDFC MF Index Solutions Factsheet - June 2026_1.pdf</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1002,14 +1002,13 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>downloads\Helios_Mutual_Fund_Helios-Mutual-Fund-Factsheet-Jun26.pdf
-downloads\Helios_Mutual_Fund_Performance-Helios-Factsheet_Jun26.pdf</t>
+          <t>downloads\Helios_Mutual_Fund_helios-mutual-fund-factsheet-jul26.pdf</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1036,7 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1059,13 +1058,13 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>downloads\ICICI_Prudential_Mutual_Fund_Complete Factsheet June 2026.pdf</t>
+          <t>downloads\ICICI_Prudential_Mutual_Fund_Complete Factsheet July 2026.pdf</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1092,7 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1120,7 @@
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1148,7 @@
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1176,7 @@
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1204,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1232,7 @@
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1260,7 @@
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1289,7 @@
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1318,7 @@
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1347,7 @@
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1375,7 @@
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1398,13 +1397,13 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>downloads\NJ_Mutual_Fund_NJ-AMC-Factsheet-June-2026-20260710060515.pdf</t>
+          <t>downloads\NJ_Mutual_Fund_NJ-MF-Factsheet-July-2026-20260806102447.pdf</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1431,7 @@
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1459,7 @@
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1487,7 @@
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1515,7 @@
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1538,13 +1537,13 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>downloads\Quantum_Mutual_Fund_ed2d9740-a26e-4f5b-8c6c-d4c102293708.pdf</t>
+          <t>downloads\Quantum_Mutual_Fund_5d2d6fde-bc37-4ce2-9318-73b6756d9652.pdf</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1572,7 @@
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1601,7 @@
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1629,7 @@
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1657,7 @@
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1685,7 @@
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1713,7 @@
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1736,13 +1735,13 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>downloads\The_Wealth_Company_Mutual_Fund_Factsheet_as_on_30_06_2026_1946ab499d.pdf</t>
+          <t>downloads\The_Wealth_Company_Mutual_Fund_The_Wealth_Company_Factsheet_July_2026_a58370ee64.pdf</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1769,7 @@
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1797,7 @@
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1825,7 @@
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1853,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1881,7 @@
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1909,7 @@
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:48:28</t>
+          <t>2026-08-07 00:21:25</t>
         </is>
       </c>
     </row>
